--- a/www/terminologies/ValueSet-jdv-motif-echographie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-motif-echographie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141839</t>
+    <t>20260220142104</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:39+01:00</t>
+    <t>2026-02-20T14:21:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -116,12 +116,6 @@
     <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
   </si>
   <si>
-    <t>MED-107</t>
-  </si>
-  <si>
-    <t>Implant</t>
-  </si>
-  <si>
     <t>GEN-092.01.07</t>
   </si>
   <si>
@@ -129,6 +123,12 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+  </si>
+  <si>
+    <t>2282003</t>
+  </si>
+  <si>
+    <t>prothèse mammaire</t>
   </si>
   <si>
     <t>161615003</t>
@@ -447,6 +447,52 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -464,18 +510,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -491,52 +537,6 @@
         <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s" s="2">
         <v>40</v>
       </c>
     </row>

--- a/www/terminologies/ValueSet-jdv-motif-echographie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-motif-echographie-cisis.xlsx
@@ -9,13 +9,12 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142104</t>
+    <t>20260311144904</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:04+01:00</t>
+    <t>2026-03-11T14:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -101,10 +100,10 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>C94305</t>
-  </si>
-  <si>
-    <t>densité mammaire</t>
+    <t>GEN-092.01.07</t>
+  </si>
+  <si>
+    <t>Autre motif d'échographie</t>
   </si>
   <si>
     <t/>
@@ -113,16 +112,13 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
-  </si>
-  <si>
-    <t>GEN-092.01.07</t>
-  </si>
-  <si>
-    <t>Autre motif d'échographie</t>
-  </si>
-  <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+  </si>
+  <si>
+    <t>129793001</t>
+  </si>
+  <si>
+    <t>densité du sein à la mammographie</t>
   </si>
   <si>
     <t>2282003</t>
@@ -447,7 +443,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -472,72 +468,34 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>40</v>
+      <c r="B6" t="s" s="2">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-jdv-motif-echographie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-motif-echographie-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144904</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:04+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-motif-echographie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-motif-echographie-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150251</t>
+    <t>20260619134043</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:51+01:00</t>
+    <t>2026-06-19T13:40:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-motif-echographie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-motif-echographie-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134043</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:43+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-motif-echographie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-motif-echographie-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134043</t>
+    <t>20260716085852</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:43+01:00</t>
+    <t>2026-07-16T08:58:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
